--- a/utils/monday_sprint_sprint_2025-22.xlsx
+++ b/utils/monday_sprint_sprint_2025-22.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1272" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1272" uniqueCount="255">
   <si>
     <t>Ticket</t>
   </si>
@@ -216,406 +216,409 @@
     <t>26/09/2025</t>
   </si>
   <si>
+    <t>20/02/2026</t>
+  </si>
+  <si>
+    <t>Semana 4</t>
+  </si>
+  <si>
+    <t>Setembro</t>
+  </si>
+  <si>
+    <t>34776</t>
+  </si>
+  <si>
+    <t>Correção informações Registro 1100</t>
+  </si>
+  <si>
+    <t>34738</t>
+  </si>
+  <si>
+    <t>ATUALIZAÇÃO DE TABELAS DO CPP22</t>
+  </si>
+  <si>
+    <t>32141</t>
+  </si>
+  <si>
+    <t>Cadastro de Embalagem no CPP</t>
+  </si>
+  <si>
+    <t>Bom dia, Flavio, Gentileza criar na tela do CPP 03 campos. * Código da Embalagem: * Dimensão: * Peso Embalagem: O preenchimento será feito de duas formas: * O histórico vamos enviar uma lista com o modelo e as informações para a atualização de todos os vigentes. * Os novos modelos o Diego irá preenc</t>
+  </si>
+  <si>
+    <t>Djalma Machado</t>
+  </si>
+  <si>
+    <t>06/06/2025</t>
+  </si>
+  <si>
+    <t>Junho</t>
+  </si>
+  <si>
+    <t>34741</t>
+  </si>
+  <si>
+    <t>Consulta movimentação - Tempo de entrega</t>
+  </si>
+  <si>
+    <t>34740</t>
+  </si>
+  <si>
+    <t>CAMPO DE OBSERVAÇÕES TRATAMENTO TÉRMICO AP119 X CPP</t>
+  </si>
+  <si>
+    <t>34742</t>
+  </si>
+  <si>
+    <t>Lista suspensa - Contentores</t>
+  </si>
+  <si>
+    <t>34336</t>
+  </si>
+  <si>
+    <t>DIÁRIO DE BORDO</t>
+  </si>
+  <si>
+    <t>Bom dia, Favor atualizar o sistema de Diário de Bordo [UCPP221Y] no CPP para que permita mais opções de cadastros e consultas conforme campos existentes da tela WCPP22K, exceto os riscados na imagem abaixo, e com duas opções a mais sendo "Peso Unitário" e "Tipo de Produção": At.te</t>
+  </si>
+  <si>
+    <t>Willian Gabriel Paixão dos Santos</t>
+  </si>
+  <si>
+    <t>ADH</t>
+  </si>
+  <si>
+    <t>25/09/2025</t>
+  </si>
+  <si>
+    <t>33790</t>
+  </si>
+  <si>
+    <t>Dados divergentes tempo padrão - CPP e QlikSense</t>
+  </si>
+  <si>
+    <t>29853</t>
+  </si>
+  <si>
+    <t>WMS - Sistema de Picking - Distribuição de Estoque em carteira</t>
+  </si>
+  <si>
+    <t>Boa tarde Conforme conversamos, precisamos de um sistema dentro do WMS que faça a distribuição em tempo real do saldo do Estoque com a carteira. Conforme é realizado o faturamento, a carteira seja atualizada em tempo real, bem como a entrada e estorno do material. O sistema deve fornecer um relatóri</t>
+  </si>
+  <si>
+    <t>31/01/2025</t>
+  </si>
+  <si>
+    <t>19/05/2026</t>
+  </si>
+  <si>
+    <t>Semana 5</t>
+  </si>
+  <si>
+    <t>Janeiro</t>
+  </si>
+  <si>
+    <t>34755</t>
+  </si>
+  <si>
+    <t>Qlik | Base de Proformas + Parcelas &amp; Registro de Cambio de Adiantamento de Proforma</t>
+  </si>
+  <si>
+    <t>33772</t>
+  </si>
+  <si>
+    <t>Melhoria no cadastramento dos tempos padrões - CPP</t>
+  </si>
+  <si>
+    <t>34689</t>
+  </si>
+  <si>
+    <t>CPPs LIGA 101XX</t>
+  </si>
+  <si>
+    <t>34693</t>
+  </si>
+  <si>
+    <t>Motivos de retrabalho da moldagem</t>
+  </si>
+  <si>
+    <t>34692</t>
+  </si>
+  <si>
+    <t>Inserir pergunta - Aplicação Check-List USINAGEM</t>
+  </si>
+  <si>
+    <t>34687</t>
+  </si>
+  <si>
+    <t>Filtro função no irog</t>
+  </si>
+  <si>
+    <t>34751</t>
+  </si>
+  <si>
+    <t>Correção</t>
+  </si>
+  <si>
+    <t>Falta de apontamentos - Aplicação IROG Usinagem</t>
+  </si>
+  <si>
+    <t>34710</t>
+  </si>
+  <si>
+    <t>Erro em OTF</t>
+  </si>
+  <si>
+    <t>34073</t>
+  </si>
+  <si>
+    <t>Callback em aplicações WEB</t>
+  </si>
+  <si>
+    <t>Implantação</t>
+  </si>
+  <si>
+    <t>34733</t>
+  </si>
+  <si>
+    <t>Melhoria WMS Materiais endereçados</t>
+  </si>
+  <si>
+    <t>33360</t>
+  </si>
+  <si>
+    <t>Auditoria MPO, PID e Checklist</t>
+  </si>
+  <si>
+    <t>34730</t>
+  </si>
+  <si>
+    <t>Melhoria no sistema de pré-lista WMS</t>
+  </si>
+  <si>
+    <t>34731</t>
+  </si>
+  <si>
+    <t>Ajuste no relatório de inventario</t>
+  </si>
+  <si>
+    <t>34729</t>
+  </si>
+  <si>
+    <t>Melhoria WMS assinatura digital</t>
+  </si>
+  <si>
+    <t>32873</t>
+  </si>
+  <si>
+    <t>Dados Pgto por Invoice</t>
+  </si>
+  <si>
+    <t>24746</t>
+  </si>
+  <si>
+    <t>Integração de faturamentos com eventos</t>
+  </si>
+  <si>
+    <t>34732</t>
+  </si>
+  <si>
+    <t>Ajuste no inventario WMS</t>
+  </si>
+  <si>
+    <t>29476</t>
+  </si>
+  <si>
+    <t>Qlik Sense - Dados Parcelas Invoice e Pgto</t>
+  </si>
+  <si>
+    <t>34665</t>
+  </si>
+  <si>
+    <t>Sistema de Consulta MPO</t>
+  </si>
+  <si>
+    <t>34109</t>
+  </si>
+  <si>
+    <t>Melhorias Sistema Manutenção</t>
+  </si>
+  <si>
+    <t>33662</t>
+  </si>
+  <si>
+    <t>Controle de documentação de exportação</t>
+  </si>
+  <si>
+    <t>34682</t>
+  </si>
+  <si>
+    <t>Registro campanha forno Arco</t>
+  </si>
+  <si>
+    <t>33632</t>
+  </si>
+  <si>
+    <t>Cálculo de carga - Sistema de corridas - Reunião</t>
+  </si>
+  <si>
+    <t>34323</t>
+  </si>
+  <si>
+    <t>Incluir informação - tela de Log Sequencias</t>
+  </si>
+  <si>
+    <t>34728</t>
+  </si>
+  <si>
+    <t>Ajustes na tela de coleta de assinatura digital</t>
+  </si>
+  <si>
+    <t>34635</t>
+  </si>
+  <si>
+    <t>Melhoria B. I.</t>
+  </si>
+  <si>
+    <t>34727</t>
+  </si>
+  <si>
+    <t>Problema na alocação de materiais no sistema de Pré-Lista Web</t>
+  </si>
+  <si>
+    <t>33333</t>
+  </si>
+  <si>
+    <t>Teste com Trigger - Checagem do fechamento do custo</t>
+  </si>
+  <si>
+    <t>Homologação</t>
+  </si>
+  <si>
+    <t>34725</t>
+  </si>
+  <si>
+    <t>Solicitação de melhoria no sistema de pré-lista web</t>
+  </si>
+  <si>
+    <t>34475</t>
+  </si>
+  <si>
+    <t>CRIAÇÃO DE FLUXO ( RETRABALHO BRUTO REB VI )</t>
+  </si>
+  <si>
+    <t>34726</t>
+  </si>
+  <si>
+    <t>Inconsistência de saldos entre WMS e ERP na pré-lista WEB</t>
+  </si>
+  <si>
+    <t>34758</t>
+  </si>
+  <si>
+    <t>Alteração na tela Gestão a Vista "Controle de PO em aberto"</t>
+  </si>
+  <si>
+    <t>34615</t>
+  </si>
+  <si>
+    <t>Inclusão de informação no momento da exclusão de NF da portaria</t>
+  </si>
+  <si>
+    <t>34549</t>
+  </si>
+  <si>
+    <t>Travamento do registro</t>
+  </si>
+  <si>
+    <t>Bom dia, Colocar travamento de finalização do registro de fechamento da moldagem USE e ULE. Registro de fechamento somente pode ser finalizado quando o registro de macharia estiver finalizado. Att.</t>
+  </si>
+  <si>
+    <t>Darlan Pressi</t>
+  </si>
+  <si>
+    <t>07/10/2025</t>
+  </si>
+  <si>
+    <t>06/03/2026</t>
+  </si>
+  <si>
+    <t>Manter data/hora de inclusão e data/Hora de alteração.</t>
+  </si>
+  <si>
+    <t>34542</t>
+  </si>
+  <si>
+    <t>Sistema Indicadores GIQ</t>
+  </si>
+  <si>
+    <t>34432</t>
+  </si>
+  <si>
+    <t>Modificar Painel Manipuladores para APON3</t>
+  </si>
+  <si>
+    <t>33130</t>
+  </si>
+  <si>
+    <t>Integração CRM - Carga Ofertas</t>
+  </si>
+  <si>
+    <t>Laura Herrmann Schmickler</t>
+  </si>
+  <si>
+    <t>28/07/2025</t>
+  </si>
+  <si>
+    <t>Julho</t>
+  </si>
+  <si>
+    <t>34724</t>
+  </si>
+  <si>
+    <t>Solicitação de melhoria no sistema de inventário – Embalagens Magayver</t>
+  </si>
+  <si>
+    <t>34697</t>
+  </si>
+  <si>
+    <t>Conferencia de volumes NF/pre-embarque</t>
+  </si>
+  <si>
+    <t>33965</t>
+  </si>
+  <si>
+    <t>Apontamento de moldes Carrossel</t>
+  </si>
+  <si>
+    <t>Boa tarde, Necessário criar no apontamento para carrossel, identificando a sequência e se são as partes superiores e Inferiores. Att.</t>
+  </si>
+  <si>
+    <t>Matheus Rodrigues de Almeida</t>
+  </si>
+  <si>
+    <t>05/09/2025</t>
+  </si>
+  <si>
+    <t>33660</t>
+  </si>
+  <si>
+    <t>Apontamento por botoeiras na Carrossel</t>
+  </si>
+  <si>
+    <t>34012</t>
+  </si>
+  <si>
+    <t>Painel de indicadores + Melhorias - Sistema Manutenção</t>
+  </si>
+  <si>
+    <t>Boa tarde, Estamos com uma ação vinculada ao projeto Produttare e algumas frentes de implementação de indicadores na área de Manutenção. Precisamos da ajuda do time de TI para iniciarmos com um painel de indicadores com as seguintes sugestões para implementação via Qlikview. Indicador MDT (Mean down</t>
+  </si>
+  <si>
+    <t>09/09/2025</t>
+  </si>
+  <si>
     <t>25/02/2026</t>
-  </si>
-  <si>
-    <t>Semana 4</t>
-  </si>
-  <si>
-    <t>Setembro</t>
-  </si>
-  <si>
-    <t>34776</t>
-  </si>
-  <si>
-    <t>Correção informações Registro 1100</t>
-  </si>
-  <si>
-    <t>34738</t>
-  </si>
-  <si>
-    <t>ATUALIZAÇÃO DE TABELAS DO CPP22</t>
-  </si>
-  <si>
-    <t>32141</t>
-  </si>
-  <si>
-    <t>Cadastro de Embalagem no CPP</t>
-  </si>
-  <si>
-    <t>Bom dia, Flavio, Gentileza criar na tela do CPP 03 campos. * Código da Embalagem: * Dimensão: * Peso Embalagem: O preenchimento será feito de duas formas: * O histórico vamos enviar uma lista com o modelo e as informações para a atualização de todos os vigentes. * Os novos modelos o Diego irá preenc</t>
-  </si>
-  <si>
-    <t>Djalma Machado</t>
-  </si>
-  <si>
-    <t>06/06/2025</t>
-  </si>
-  <si>
-    <t>Junho</t>
-  </si>
-  <si>
-    <t>34741</t>
-  </si>
-  <si>
-    <t>Consulta movimentação - Tempo de entrega</t>
-  </si>
-  <si>
-    <t>34740</t>
-  </si>
-  <si>
-    <t>CAMPO DE OBSERVAÇÕES TRATAMENTO TÉRMICO AP119 X CPP</t>
-  </si>
-  <si>
-    <t>34742</t>
-  </si>
-  <si>
-    <t>Lista suspensa - Contentores</t>
-  </si>
-  <si>
-    <t>34336</t>
-  </si>
-  <si>
-    <t>DIÁRIO DE BORDO</t>
-  </si>
-  <si>
-    <t>Bom dia, Favor atualizar o sistema de Diário de Bordo [UCPP221Y] no CPP para que permita mais opções de cadastros e consultas conforme campos existentes da tela WCPP22K, exceto os riscados na imagem abaixo, e com duas opções a mais sendo "Peso Unitário" e "Tipo de Produção": At.te</t>
-  </si>
-  <si>
-    <t>Willian Gabriel Paixão dos Santos</t>
-  </si>
-  <si>
-    <t>ADH</t>
-  </si>
-  <si>
-    <t>25/09/2025</t>
-  </si>
-  <si>
-    <t>33790</t>
-  </si>
-  <si>
-    <t>Dados divergentes tempo padrão - CPP e QlikSense</t>
-  </si>
-  <si>
-    <t>29853</t>
-  </si>
-  <si>
-    <t>WMS - Sistema de Picking - Distribuição de Estoque em carteira</t>
-  </si>
-  <si>
-    <t>Boa tarde Conforme conversamos, precisamos de um sistema dentro do WMS que faça a distribuição em tempo real do saldo do Estoque com a carteira. Conforme é realizado o faturamento, a carteira seja atualizada em tempo real, bem como a entrada e estorno do material. O sistema deve fornecer um relatóri</t>
-  </si>
-  <si>
-    <t>31/01/2025</t>
-  </si>
-  <si>
-    <t>Semana 5</t>
-  </si>
-  <si>
-    <t>Janeiro</t>
-  </si>
-  <si>
-    <t>34755</t>
-  </si>
-  <si>
-    <t>Qlik | Base de Proformas + Parcelas &amp; Registro de Cambio de Adiantamento de Proforma</t>
-  </si>
-  <si>
-    <t>33772</t>
-  </si>
-  <si>
-    <t>Melhoria no cadastramento dos tempos padrões - CPP</t>
-  </si>
-  <si>
-    <t>34689</t>
-  </si>
-  <si>
-    <t>CPPs LIGA 101XX</t>
-  </si>
-  <si>
-    <t>34693</t>
-  </si>
-  <si>
-    <t>Motivos de retrabalho da moldagem</t>
-  </si>
-  <si>
-    <t>34692</t>
-  </si>
-  <si>
-    <t>Inserir pergunta - Aplicação Check-List USINAGEM</t>
-  </si>
-  <si>
-    <t>34687</t>
-  </si>
-  <si>
-    <t>Filtro função no irog</t>
-  </si>
-  <si>
-    <t>34751</t>
-  </si>
-  <si>
-    <t>Correção</t>
-  </si>
-  <si>
-    <t>Falta de apontamentos - Aplicação IROG Usinagem</t>
-  </si>
-  <si>
-    <t>34710</t>
-  </si>
-  <si>
-    <t>Erro em OTF</t>
-  </si>
-  <si>
-    <t>34073</t>
-  </si>
-  <si>
-    <t>Callback em aplicações WEB</t>
-  </si>
-  <si>
-    <t>Implantação</t>
-  </si>
-  <si>
-    <t>34733</t>
-  </si>
-  <si>
-    <t>Melhoria WMS Materiais endereçados</t>
-  </si>
-  <si>
-    <t>33360</t>
-  </si>
-  <si>
-    <t>Auditoria MPO, PID e Checklist</t>
-  </si>
-  <si>
-    <t>34730</t>
-  </si>
-  <si>
-    <t>Melhoria no sistema de pré-lista WMS</t>
-  </si>
-  <si>
-    <t>34731</t>
-  </si>
-  <si>
-    <t>Ajuste no relatório de inventario</t>
-  </si>
-  <si>
-    <t>34729</t>
-  </si>
-  <si>
-    <t>Melhoria WMS assinatura digital</t>
-  </si>
-  <si>
-    <t>32873</t>
-  </si>
-  <si>
-    <t>Dados Pgto por Invoice</t>
-  </si>
-  <si>
-    <t>24746</t>
-  </si>
-  <si>
-    <t>Integração de faturamentos com eventos</t>
-  </si>
-  <si>
-    <t>34732</t>
-  </si>
-  <si>
-    <t>Ajuste no inventario WMS</t>
-  </si>
-  <si>
-    <t>29476</t>
-  </si>
-  <si>
-    <t>Qlik Sense - Dados Parcelas Invoice e Pgto</t>
-  </si>
-  <si>
-    <t>34665</t>
-  </si>
-  <si>
-    <t>Sistema de Consulta MPO</t>
-  </si>
-  <si>
-    <t>34109</t>
-  </si>
-  <si>
-    <t>Melhorias Sistema Manutenção</t>
-  </si>
-  <si>
-    <t>33662</t>
-  </si>
-  <si>
-    <t>Controle de documentação de exportação</t>
-  </si>
-  <si>
-    <t>34682</t>
-  </si>
-  <si>
-    <t>Registro campanha forno Arco</t>
-  </si>
-  <si>
-    <t>33632</t>
-  </si>
-  <si>
-    <t>Cálculo de carga - Sistema de corridas - Reunião</t>
-  </si>
-  <si>
-    <t>34323</t>
-  </si>
-  <si>
-    <t>Incluir informação - tela de Log Sequencias</t>
-  </si>
-  <si>
-    <t>34728</t>
-  </si>
-  <si>
-    <t>Ajustes na tela de coleta de assinatura digital</t>
-  </si>
-  <si>
-    <t>34635</t>
-  </si>
-  <si>
-    <t>Melhoria B. I.</t>
-  </si>
-  <si>
-    <t>34727</t>
-  </si>
-  <si>
-    <t>Problema na alocação de materiais no sistema de Pré-Lista Web</t>
-  </si>
-  <si>
-    <t>33333</t>
-  </si>
-  <si>
-    <t>Teste com Trigger - Checagem do fechamento do custo</t>
-  </si>
-  <si>
-    <t>Homologação</t>
-  </si>
-  <si>
-    <t>34725</t>
-  </si>
-  <si>
-    <t>Solicitação de melhoria no sistema de pré-lista web</t>
-  </si>
-  <si>
-    <t>34475</t>
-  </si>
-  <si>
-    <t>CRIAÇÃO DE FLUXO ( RETRABALHO BRUTO REB VI )</t>
-  </si>
-  <si>
-    <t>34726</t>
-  </si>
-  <si>
-    <t>Inconsistência de saldos entre WMS e ERP na pré-lista WEB</t>
-  </si>
-  <si>
-    <t>34758</t>
-  </si>
-  <si>
-    <t>Alteração na tela Gestão a Vista "Controle de PO em aberto"</t>
-  </si>
-  <si>
-    <t>34615</t>
-  </si>
-  <si>
-    <t>Inclusão de informação no momento da exclusão de NF da portaria</t>
-  </si>
-  <si>
-    <t>34549</t>
-  </si>
-  <si>
-    <t>Travamento do registro</t>
-  </si>
-  <si>
-    <t>Bom dia, Colocar travamento de finalização do registro de fechamento da moldagem USE e ULE. Registro de fechamento somente pode ser finalizado quando o registro de macharia estiver finalizado. Att.</t>
-  </si>
-  <si>
-    <t>Darlan Pressi</t>
-  </si>
-  <si>
-    <t>07/10/2025</t>
-  </si>
-  <si>
-    <t>09/03/2026</t>
-  </si>
-  <si>
-    <t>Manter data/hora de inclusão e data/Hora de alteração.</t>
-  </si>
-  <si>
-    <t>34542</t>
-  </si>
-  <si>
-    <t>Sistema Indicadores GIQ</t>
-  </si>
-  <si>
-    <t>34432</t>
-  </si>
-  <si>
-    <t>Modificar Painel Manipuladores para APON3</t>
-  </si>
-  <si>
-    <t>33130</t>
-  </si>
-  <si>
-    <t>Integração CRM - Carga Ofertas</t>
-  </si>
-  <si>
-    <t>Laura Herrmann Schmickler</t>
-  </si>
-  <si>
-    <t>28/07/2025</t>
-  </si>
-  <si>
-    <t>Julho</t>
-  </si>
-  <si>
-    <t>34724</t>
-  </si>
-  <si>
-    <t>Solicitação de melhoria no sistema de inventário – Embalagens Magayver</t>
-  </si>
-  <si>
-    <t>34697</t>
-  </si>
-  <si>
-    <t>Conferencia de volumes NF/pre-embarque</t>
-  </si>
-  <si>
-    <t>33965</t>
-  </si>
-  <si>
-    <t>Apontamento de moldes Carrossel</t>
-  </si>
-  <si>
-    <t>Boa tarde, Necessário criar no apontamento para carrossel, identificando a sequência e se são as partes superiores e Inferiores. Att.</t>
-  </si>
-  <si>
-    <t>Matheus Rodrigues de Almeida</t>
-  </si>
-  <si>
-    <t>05/09/2025</t>
-  </si>
-  <si>
-    <t>33660</t>
-  </si>
-  <si>
-    <t>Apontamento por botoeiras na Carrossel</t>
-  </si>
-  <si>
-    <t>34012</t>
-  </si>
-  <si>
-    <t>Painel de indicadores + Melhorias - Sistema Manutenção</t>
-  </si>
-  <si>
-    <t>Boa tarde, Estamos com uma ação vinculada ao projeto Produttare e algumas frentes de implementação de indicadores na área de Manutenção. Precisamos da ajuda do time de TI para iniciarmos com um painel de indicadores com as seguintes sugestões para implementação via Qlikview. Indicador MDT (Mean down</t>
-  </si>
-  <si>
-    <t>09/09/2025</t>
-  </si>
-  <si>
-    <t>02/03/2026</t>
   </si>
   <si>
     <t>Filtro máquinas críticas</t>
@@ -2295,21 +2298,21 @@
         <v>97</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>17</v>
+        <v>98</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>34</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>15</v>
@@ -2321,10 +2324,10 @@
         <v>17</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>27</v>
@@ -2353,7 +2356,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>15</v>
@@ -2365,10 +2368,10 @@
         <v>17</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>27</v>
@@ -2397,7 +2400,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>15</v>
@@ -2409,10 +2412,10 @@
         <v>17</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>19</v>
@@ -2441,7 +2444,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>15</v>
@@ -2453,10 +2456,10 @@
         <v>17</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>19</v>
@@ -2485,7 +2488,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>15</v>
@@ -2497,10 +2500,10 @@
         <v>17</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>19</v>
@@ -2529,7 +2532,7 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>15</v>
@@ -2541,10 +2544,10 @@
         <v>17</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>19</v>
@@ -2573,22 +2576,22 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>19</v>
@@ -2617,22 +2620,22 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>19</v>
@@ -2661,7 +2664,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>15</v>
@@ -2673,10 +2676,10 @@
         <v>17</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>19</v>
@@ -2694,7 +2697,7 @@
         <v>17</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="M34" s="2" t="s">
         <v>24</v>
@@ -2705,7 +2708,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>15</v>
@@ -2717,10 +2720,10 @@
         <v>17</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>54</v>
@@ -2749,22 +2752,22 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>19</v>
@@ -2793,7 +2796,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>15</v>
@@ -2805,10 +2808,10 @@
         <v>17</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>54</v>
@@ -2837,7 +2840,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>15</v>
@@ -2849,10 +2852,10 @@
         <v>17</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>54</v>
@@ -2881,7 +2884,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>15</v>
@@ -2893,10 +2896,10 @@
         <v>17</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>54</v>
@@ -2925,7 +2928,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>15</v>
@@ -2937,10 +2940,10 @@
         <v>17</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>27</v>
@@ -2969,7 +2972,7 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>15</v>
@@ -2981,10 +2984,10 @@
         <v>17</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>19</v>
@@ -3013,7 +3016,7 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>15</v>
@@ -3025,10 +3028,10 @@
         <v>17</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>54</v>
@@ -3057,7 +3060,7 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>15</v>
@@ -3069,10 +3072,10 @@
         <v>17</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>27</v>
@@ -3101,7 +3104,7 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>15</v>
@@ -3113,10 +3116,10 @@
         <v>17</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>19</v>
@@ -3134,7 +3137,7 @@
         <v>17</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="M44" s="2" t="s">
         <v>24</v>
@@ -3145,7 +3148,7 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>15</v>
@@ -3157,10 +3160,10 @@
         <v>17</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>19</v>
@@ -3189,7 +3192,7 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>15</v>
@@ -3201,10 +3204,10 @@
         <v>17</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>19</v>
@@ -3233,7 +3236,7 @@
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>15</v>
@@ -3245,10 +3248,10 @@
         <v>17</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>19</v>
@@ -3277,7 +3280,7 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>15</v>
@@ -3289,10 +3292,10 @@
         <v>17</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>19</v>
@@ -3321,7 +3324,7 @@
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>15</v>
@@ -3333,10 +3336,10 @@
         <v>17</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>19</v>
@@ -3365,7 +3368,7 @@
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>15</v>
@@ -3377,10 +3380,10 @@
         <v>17</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>54</v>
@@ -3409,7 +3412,7 @@
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>15</v>
@@ -3421,10 +3424,10 @@
         <v>17</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>19</v>
@@ -3453,7 +3456,7 @@
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>15</v>
@@ -3465,10 +3468,10 @@
         <v>17</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>54</v>
@@ -3497,7 +3500,7 @@
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>15</v>
@@ -3509,10 +3512,10 @@
         <v>17</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>19</v>
@@ -3530,7 +3533,7 @@
         <v>17</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M53" s="2" t="s">
         <v>24</v>
@@ -3541,7 +3544,7 @@
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>15</v>
@@ -3553,10 +3556,10 @@
         <v>17</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>54</v>
@@ -3585,7 +3588,7 @@
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>15</v>
@@ -3597,10 +3600,10 @@
         <v>17</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>19</v>
@@ -3629,7 +3632,7 @@
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>15</v>
@@ -3641,10 +3644,10 @@
         <v>17</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>54</v>
@@ -3673,7 +3676,7 @@
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>15</v>
@@ -3685,10 +3688,10 @@
         <v>17</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>19</v>
@@ -3717,7 +3720,7 @@
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>15</v>
@@ -3729,10 +3732,10 @@
         <v>17</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>19</v>
@@ -3761,7 +3764,7 @@
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>15</v>
@@ -3773,28 +3776,28 @@
         <v>40</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>90</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="M59" s="2" t="s">
         <v>21</v>
@@ -3805,7 +3808,7 @@
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>15</v>
@@ -3817,10 +3820,10 @@
         <v>17</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>19</v>
@@ -3838,7 +3841,7 @@
         <v>17</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M60" s="2" t="s">
         <v>24</v>
@@ -3849,7 +3852,7 @@
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>15</v>
@@ -3861,10 +3864,10 @@
         <v>17</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>19</v>
@@ -3893,7 +3896,7 @@
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>15</v>
@@ -3905,10 +3908,10 @@
         <v>17</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>19</v>
@@ -3937,7 +3940,7 @@
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>15</v>
@@ -3949,7 +3952,7 @@
         <v>40</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>17</v>
@@ -3958,13 +3961,13 @@
         <v>27</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I63" s="2" t="s">
         <v>44</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K63" s="2" t="s">
         <v>17</v>
@@ -3976,12 +3979,12 @@
         <v>68</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>15</v>
@@ -3993,10 +3996,10 @@
         <v>17</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>19</v>
@@ -4025,7 +4028,7 @@
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>15</v>
@@ -4037,10 +4040,10 @@
         <v>17</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>19</v>
@@ -4058,7 +4061,7 @@
         <v>17</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="M65" s="2" t="s">
         <v>24</v>
@@ -4069,7 +4072,7 @@
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>15</v>
@@ -4081,22 +4084,22 @@
         <v>40</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>27</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I66" s="2" t="s">
         <v>44</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K66" s="2" t="s">
         <v>17</v>
@@ -4113,7 +4116,7 @@
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>15</v>
@@ -4125,10 +4128,10 @@
         <v>17</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>19</v>
@@ -4157,7 +4160,7 @@
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>15</v>
@@ -4169,10 +4172,10 @@
         <v>40</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>19</v>
@@ -4184,10 +4187,10 @@
         <v>44</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L68" s="2" t="s">
         <v>34</v>
@@ -4213,10 +4216,10 @@
         <v>17</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>27</v>
@@ -4257,10 +4260,10 @@
         <v>17</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>27</v>
@@ -4289,22 +4292,22 @@
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>27</v>
@@ -4345,10 +4348,10 @@
         <v>17</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>27</v>
@@ -4377,7 +4380,7 @@
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>15</v>
@@ -4389,10 +4392,10 @@
         <v>17</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>19</v>
@@ -4421,7 +4424,7 @@
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>15</v>
@@ -4433,10 +4436,10 @@
         <v>17</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>19</v>
@@ -4465,7 +4468,7 @@
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>15</v>
@@ -4477,10 +4480,10 @@
         <v>17</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>19</v>
@@ -4509,7 +4512,7 @@
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>15</v>
@@ -4521,10 +4524,10 @@
         <v>17</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>19</v>
@@ -4553,7 +4556,7 @@
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>15</v>
@@ -4565,10 +4568,10 @@
         <v>17</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>19</v>
@@ -4597,7 +4600,7 @@
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>15</v>
@@ -4609,10 +4612,10 @@
         <v>17</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>19</v>
@@ -4641,7 +4644,7 @@
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>15</v>
@@ -4653,10 +4656,10 @@
         <v>17</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>19</v>
@@ -4697,10 +4700,10 @@
         <v>17</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>19</v>
@@ -4729,7 +4732,7 @@
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>15</v>
@@ -4741,10 +4744,10 @@
         <v>17</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>19</v>
@@ -4773,7 +4776,7 @@
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>15</v>
@@ -4785,10 +4788,10 @@
         <v>17</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>19</v>
@@ -4817,7 +4820,7 @@
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>15</v>
@@ -4829,10 +4832,10 @@
         <v>17</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>19</v>
@@ -4861,7 +4864,7 @@
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>15</v>
@@ -4873,10 +4876,10 @@
         <v>17</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>19</v>
@@ -4905,7 +4908,7 @@
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>15</v>
@@ -4917,10 +4920,10 @@
         <v>17</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>19</v>
@@ -4941,7 +4944,7 @@
         <v>20</v>
       </c>
       <c r="M85" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="N85" s="2" t="s">
         <v>17</v>
@@ -4960,23 +4963,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -4984,16 +4987,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -5012,7 +5015,7 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -5025,7 +5028,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K23">
         <v>4</v>
@@ -5033,7 +5036,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -5064,12 +5067,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B2">
         <v>84</v>
@@ -5093,25 +5096,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -5128,13 +5131,13 @@
         <v>72</v>
       </c>
       <c r="G10" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -5149,7 +5152,7 @@
         <v>21</v>
       </c>
       <c r="Q10">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="4:17" x14ac:dyDescent="0.25">
@@ -5166,7 +5169,7 @@
         <v>16</v>
       </c>
       <c r="J11" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K11">
         <v>84</v>
@@ -5181,12 +5184,12 @@
         <v>28</v>
       </c>
       <c r="Q11">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D12" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E12">
         <v>3</v>
@@ -5198,7 +5201,7 @@
         <v>57</v>
       </c>
       <c r="M12" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -5207,12 +5210,12 @@
         <v>24</v>
       </c>
       <c r="Q12">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -5233,24 +5236,24 @@
         <v>68</v>
       </c>
       <c r="Q13">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="7:17" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="M14" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N14">
         <v>4</v>
       </c>
       <c r="P14" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q14">
         <v>1</v>
@@ -5258,7 +5261,7 @@
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="N15">
         <v>2</v>
@@ -5266,7 +5269,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -5274,7 +5277,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -5282,7 +5285,7 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
@@ -5293,7 +5296,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -5307,7 +5310,7 @@
         <v>15</v>
       </c>
       <c r="F21" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>95</v>
@@ -5321,7 +5324,7 @@
         <v>15</v>
       </c>
       <c r="F22" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>75</v>
@@ -5329,44 +5332,44 @@
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F23" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F24" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F25" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5377,7 +5380,7 @@
         <v>15</v>
       </c>
       <c r="F26" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>87</v>
@@ -5391,7 +5394,7 @@
         <v>15</v>
       </c>
       <c r="F27" s="2">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>41</v>
@@ -5399,30 +5402,30 @@
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>62</v>
+        <v>170</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F28" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>63</v>
+        <v>171</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>169</v>
+        <v>62</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F29" s="2">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>170</v>
+        <v>63</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">

--- a/utils/monday_sprint_sprint_2025-22.xlsx
+++ b/utils/monday_sprint_sprint_2025-22.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1362" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1362" uniqueCount="273">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -60,7 +60,7 @@
     <t>Mês</t>
   </si>
   <si>
-    <t>34485</t>
+    <t>18106229112</t>
   </si>
   <si>
     <t>Setor não informado</t>
@@ -87,496 +87,526 @@
     <t>03/10/2025</t>
   </si>
   <si>
+    <t>30/10/2025</t>
+  </si>
+  <si>
+    <t>Feito</t>
+  </si>
+  <si>
+    <t>Não</t>
+  </si>
+  <si>
+    <t>Semana 1</t>
+  </si>
+  <si>
+    <t>Outubro</t>
+  </si>
+  <si>
+    <t>18212210416</t>
+  </si>
+  <si>
+    <t>Criação de Pré-lista</t>
+  </si>
+  <si>
+    <t>17/10/2025</t>
+  </si>
+  <si>
+    <t>21/10/2025</t>
+  </si>
+  <si>
+    <t>Semana 3</t>
+  </si>
+  <si>
+    <t>18137021906</t>
+  </si>
+  <si>
+    <t>Baixa de Estoque de Embalagem Expedição - Gerar requisição</t>
+  </si>
+  <si>
+    <t>Alta</t>
+  </si>
+  <si>
+    <t>08/10/2025</t>
+  </si>
+  <si>
+    <t>20/10/2025</t>
+  </si>
+  <si>
+    <t>Semana 2</t>
+  </si>
+  <si>
+    <t>18182768428</t>
+  </si>
+  <si>
+    <t>Projeto</t>
+  </si>
+  <si>
+    <t>Sistema Gestão de Ações</t>
+  </si>
+  <si>
+    <t>14/10/2025</t>
+  </si>
+  <si>
+    <t>18212649460</t>
+  </si>
+  <si>
+    <t>Altona || Consignado - Conferência Fornecedores</t>
+  </si>
+  <si>
+    <t>A fazer</t>
+  </si>
+  <si>
+    <t>18212633448</t>
+  </si>
+  <si>
+    <t>PARADAS APONTAMENTO ELETRONICO MANIPULADORES</t>
+  </si>
+  <si>
+    <t>28/10/2025</t>
+  </si>
+  <si>
+    <t>18212171997</t>
+  </si>
+  <si>
+    <t>Melhoria na assinatura digital</t>
+  </si>
+  <si>
+    <t>34720</t>
+  </si>
+  <si>
+    <t>Almoxarifado</t>
+  </si>
+  <si>
+    <t>Solicitação de serviço</t>
+  </si>
+  <si>
+    <t>Solicitação de Implementação – Coleta de Assinatura Digital para Declaração de Recebimento</t>
+  </si>
+  <si>
+    <t>Boa tarde Gostaria de solicitar a implementação de uma funcionalidade para coleta de assinatura digital referente à Declaração de Recebimento de materiais. Contexto do Processo Atual Hoje, ao receber o romaneio/cópia da nota fiscal, realizamos a seguinte sequência: 1. Acessamos o sistema no menu Con</t>
+  </si>
+  <si>
+    <t>Alex Julio Estacio</t>
+  </si>
+  <si>
+    <t>Sistemas</t>
+  </si>
+  <si>
+    <t>02/04/2026</t>
+  </si>
+  <si>
+    <t>33991</t>
+  </si>
+  <si>
+    <t>Melhoria relatório 2ª corda - Gestão a vista</t>
+  </si>
+  <si>
+    <t>Boa tarde, Foi identificado um ponto de melhoria para o relatório da segunda corda com o objetivo de gerar uma tela para gestão a vista. Conforme explicado para o Flavio, segue os pontos de necessidades: - Considerar a entrada no 8890 a partir do dia 01 de cada mês. - Considerar demanda do dia o gru</t>
+  </si>
+  <si>
+    <t>Natalia De Souza</t>
+  </si>
+  <si>
+    <t>18212622857</t>
+  </si>
+  <si>
+    <t>DESCRIÇÃO DAS OPERAÇÕES JATOS</t>
+  </si>
+  <si>
+    <t>18212182751</t>
+  </si>
+  <si>
+    <t>Solicitação de melhoria no WMS – Retenção de dados na pré-lista</t>
+  </si>
+  <si>
+    <t>Baixa</t>
+  </si>
+  <si>
+    <t>18233856195</t>
+  </si>
+  <si>
+    <t>Novos modelos para Apontamento Digital</t>
+  </si>
+  <si>
+    <t>18232241956</t>
+  </si>
+  <si>
+    <t>Chamado para revisão BI Manutenção - Chamado Principal</t>
+  </si>
+  <si>
+    <t>26/10/2025</t>
+  </si>
+  <si>
+    <t>Fazendo</t>
+  </si>
+  <si>
+    <t>18212161196</t>
+  </si>
+  <si>
+    <t>Desenvolvimento sistema Pré-lista EPI</t>
+  </si>
+  <si>
+    <t>18212661259</t>
+  </si>
+  <si>
+    <t>Lógica de ACR no sistema de manutenção - Pila 2 MP - Reunião</t>
+  </si>
+  <si>
+    <t>18233013471</t>
+  </si>
+  <si>
+    <t>Correção informações Registro 1100</t>
+  </si>
+  <si>
+    <t>18211679125</t>
+  </si>
+  <si>
+    <t>ATUALIZAÇÃO DE TABELAS DO CPP22</t>
+  </si>
+  <si>
+    <t>25/10/2025</t>
+  </si>
+  <si>
+    <t>32141</t>
+  </si>
+  <si>
+    <t>Logística</t>
+  </si>
+  <si>
+    <t>Cadastro de Embalagem no CPP</t>
+  </si>
+  <si>
+    <t>Bom dia, Flavio, Gentileza criar na tela do CPP 03 campos. * Código da Embalagem: * Dimensão: * Peso Embalagem: O preenchimento será feito de duas formas: * O histórico vamos enviar uma lista com o modelo e as informações para a atualização de todos os vigentes. * Os novos modelos o Diego irá preenc</t>
+  </si>
+  <si>
+    <t>Djalma Machado</t>
+  </si>
+  <si>
+    <t>ADH</t>
+  </si>
+  <si>
+    <t>02/06/2026</t>
+  </si>
+  <si>
+    <t>18211662625</t>
+  </si>
+  <si>
+    <t>Consulta movimentação - Tempo de entrega</t>
+  </si>
+  <si>
+    <t>22/10/2025</t>
+  </si>
+  <si>
+    <t>18211670512</t>
+  </si>
+  <si>
+    <t>CAMPO DE OBSERVAÇÕES TRATAMENTO TÉRMICO AP119 X CPP</t>
+  </si>
+  <si>
+    <t>18211644691</t>
+  </si>
+  <si>
+    <t>Lista suspensa - Contentores</t>
+  </si>
+  <si>
+    <t>34336</t>
+  </si>
+  <si>
+    <t>Engenharia</t>
+  </si>
+  <si>
+    <t>DIÁRIO DE BORDO</t>
+  </si>
+  <si>
+    <t>Bom dia, Favor atualizar o sistema de Diário de Bordo [UCPP221Y] no CPP para que permita mais opções de cadastros e consultas conforme campos existentes da tela WCPP22K, exceto os riscados na imagem abaixo, e com duas opções a mais sendo "Peso Unitário" e "Tipo de Produção": At.te</t>
+  </si>
+  <si>
+    <t>Willian Gabriel Paixão dos Santos</t>
+  </si>
+  <si>
+    <t>18212829389</t>
+  </si>
+  <si>
+    <t>Dados divergentes tempo padrão - CPP e QlikSense</t>
+  </si>
+  <si>
+    <t>29853</t>
+  </si>
+  <si>
+    <t>WMS - Sistema de Picking - Distribuição de Estoque em carteira</t>
+  </si>
+  <si>
+    <t>Boa tarde Conforme conversamos, precisamos de um sistema dentro do WMS que faça a distribuição em tempo real do saldo do Estoque com a carteira. Conforme é realizado o faturamento, a carteira seja atualizada em tempo real, bem como a entrada e estorno do material. O sistema deve fornecer um relatóri</t>
+  </si>
+  <si>
+    <t>19/05/2026</t>
+  </si>
+  <si>
+    <t>18211622537</t>
+  </si>
+  <si>
+    <t>Qlik | Base de Proformas + Parcelas &amp; Registro de Cambio de Adiantamento de Proforma</t>
+  </si>
+  <si>
+    <t>23/10/2025</t>
+  </si>
+  <si>
+    <t>18236202723</t>
+  </si>
+  <si>
+    <t>Melhoria no cadastramento dos tempos padrões - CPP</t>
+  </si>
+  <si>
+    <t>18212287268</t>
+  </si>
+  <si>
+    <t>CPPs LIGA 101XX</t>
+  </si>
+  <si>
+    <t>18212243668</t>
+  </si>
+  <si>
+    <t>Motivos de retrabalho da moldagem</t>
+  </si>
+  <si>
+    <t>18212268182</t>
+  </si>
+  <si>
+    <t>Inserir pergunta - Aplicação Check-List USINAGEM</t>
+  </si>
+  <si>
+    <t>18212306196</t>
+  </si>
+  <si>
+    <t>Filtro função no irog</t>
+  </si>
+  <si>
+    <t>18212909667</t>
+  </si>
+  <si>
+    <t>Correção</t>
+  </si>
+  <si>
+    <t>Falta de apontamentos - Aplicação IROG Usinagem</t>
+  </si>
+  <si>
+    <t>18212229307</t>
+  </si>
+  <si>
+    <t>Erro em OTF</t>
+  </si>
+  <si>
+    <t>18236202902</t>
+  </si>
+  <si>
+    <t>Callback em aplicações WEB</t>
+  </si>
+  <si>
+    <t>29/10/2025</t>
+  </si>
+  <si>
+    <t>Implantação</t>
+  </si>
+  <si>
+    <t>18211687071</t>
+  </si>
+  <si>
+    <t>Melhoria WMS Materiais endereçados</t>
+  </si>
+  <si>
+    <t>18212936395</t>
+  </si>
+  <si>
+    <t>Auditoria MPO, PID e Checklist</t>
+  </si>
+  <si>
+    <t>01/11/2025</t>
+  </si>
+  <si>
+    <t>18211721587</t>
+  </si>
+  <si>
+    <t>Melhoria no sistema de pré-lista WMS</t>
+  </si>
+  <si>
+    <t>18211707941</t>
+  </si>
+  <si>
+    <t>Ajuste no relatório de inventario</t>
+  </si>
+  <si>
+    <t>18211748808</t>
+  </si>
+  <si>
+    <t>Melhoria WMS assinatura digital</t>
+  </si>
+  <si>
+    <t>18213788831</t>
+  </si>
+  <si>
+    <t>Dados Pgto por Invoice</t>
+  </si>
+  <si>
+    <t>18236203223</t>
+  </si>
+  <si>
+    <t>Integração de faturamentos com eventos</t>
+  </si>
+  <si>
+    <t>18211698744</t>
+  </si>
+  <si>
+    <t>Ajuste no inventario WMS</t>
+  </si>
+  <si>
+    <t>18213791899</t>
+  </si>
+  <si>
+    <t>Qlik Sense - Dados Parcelas Invoice e Pgto</t>
+  </si>
+  <si>
+    <t>18212400382</t>
+  </si>
+  <si>
+    <t>Sistema de Consulta MPO</t>
+  </si>
+  <si>
+    <t>18236205413</t>
+  </si>
+  <si>
+    <t>Melhorias Sistema Manutenção</t>
+  </si>
+  <si>
+    <t>18236203160</t>
+  </si>
+  <si>
+    <t>Controle de documentação de exportação</t>
+  </si>
+  <si>
+    <t>18212324410</t>
+  </si>
+  <si>
+    <t>Registro campanha forno Arco</t>
+  </si>
+  <si>
+    <t>18236203418</t>
+  </si>
+  <si>
+    <t>Cálculo de carga - Sistema de corridas - Reunião</t>
+  </si>
+  <si>
+    <t>18236204639</t>
+  </si>
+  <si>
+    <t>Incluir informação - tela de Log Sequencias</t>
+  </si>
+  <si>
+    <t>18211767689</t>
+  </si>
+  <si>
+    <t>Ajustes na tela de coleta de assinatura digital</t>
+  </si>
+  <si>
+    <t>18212440873</t>
+  </si>
+  <si>
+    <t>Melhoria B. I.</t>
+  </si>
+  <si>
+    <t>18212104323</t>
+  </si>
+  <si>
+    <t>Problema na alocação de materiais no sistema de Pré-Lista Web</t>
+  </si>
+  <si>
+    <t>18236205850</t>
+  </si>
+  <si>
+    <t>Teste com Trigger - Checagem do fechamento do custo</t>
+  </si>
+  <si>
+    <t>Homologação</t>
+  </si>
+  <si>
+    <t>18212132109</t>
+  </si>
+  <si>
+    <t>Solicitação de melhoria no sistema de pré-lista web</t>
+  </si>
+  <si>
+    <t>18236204538</t>
+  </si>
+  <si>
+    <t>CRIAÇÃO DE FLUXO ( RETRABALHO BRUTO REB VI )</t>
+  </si>
+  <si>
+    <t>18212112816</t>
+  </si>
+  <si>
+    <t>Inconsistência de saldos entre WMS e ERP na pré-lista WEB</t>
+  </si>
+  <si>
+    <t>18213868261</t>
+  </si>
+  <si>
+    <t>Alteração na tela Gestão a Vista "Controle de PO em aberto"</t>
+  </si>
+  <si>
+    <t>18212462865</t>
+  </si>
+  <si>
+    <t>Inclusão de informação no momento da exclusão de NF da portaria</t>
+  </si>
+  <si>
+    <t>18212548240</t>
+  </si>
+  <si>
+    <t>Travamento do registro</t>
+  </si>
+  <si>
+    <t>18236203745</t>
+  </si>
+  <si>
+    <t>Manter data/hora de inclusão e data/Hora de alteração.</t>
+  </si>
+  <si>
+    <t>18212560181</t>
+  </si>
+  <si>
+    <t>Sistema Indicadores GIQ</t>
+  </si>
+  <si>
+    <t>27/10/2025</t>
+  </si>
+  <si>
+    <t>18221615933</t>
+  </si>
+  <si>
+    <t>Modificar Painel Manipuladores para APON3</t>
+  </si>
+  <si>
+    <t>33130</t>
+  </si>
+  <si>
+    <t>Comercial</t>
+  </si>
+  <si>
+    <t>Integração CRM - Carga Ofertas</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
-    <t>Feito</t>
-  </si>
-  <si>
-    <t>Não</t>
-  </si>
-  <si>
-    <t>Semana 1</t>
-  </si>
-  <si>
-    <t>Outubro</t>
-  </si>
-  <si>
-    <t>34717</t>
-  </si>
-  <si>
-    <t>Criação de Pré-lista</t>
-  </si>
-  <si>
-    <t>17/10/2025</t>
-  </si>
-  <si>
-    <t>Semana 3</t>
-  </si>
-  <si>
-    <t>32588</t>
-  </si>
-  <si>
-    <t>Baixa de Estoque de Embalagem Expedição - Gerar requisição</t>
-  </si>
-  <si>
-    <t>Alta</t>
-  </si>
-  <si>
-    <t>08/10/2025</t>
-  </si>
-  <si>
-    <t>Semana 2</t>
-  </si>
-  <si>
-    <t>30796</t>
-  </si>
-  <si>
-    <t>Projeto</t>
-  </si>
-  <si>
-    <t>Sistema Gestão de Ações</t>
-  </si>
-  <si>
-    <t>14/10/2025</t>
-  </si>
-  <si>
-    <t>34507</t>
-  </si>
-  <si>
-    <t>Altona || Consignado - Conferência Fornecedores</t>
-  </si>
-  <si>
-    <t>A fazer</t>
-  </si>
-  <si>
-    <t>Aberto</t>
-  </si>
-  <si>
-    <t>34532</t>
-  </si>
-  <si>
-    <t>PARADAS APONTAMENTO ELETRONICO MANIPULADORES</t>
-  </si>
-  <si>
-    <t>34722</t>
-  </si>
-  <si>
-    <t>Melhoria na assinatura digital</t>
-  </si>
-  <si>
-    <t>34720</t>
-  </si>
-  <si>
-    <t>Almoxarifado</t>
-  </si>
-  <si>
-    <t>Solicitação de serviço</t>
-  </si>
-  <si>
-    <t>Solicitação de Implementação – Coleta de Assinatura Digital para Declaração de Recebimento</t>
-  </si>
-  <si>
-    <t>Boa tarde Gostaria de solicitar a implementação de uma funcionalidade para coleta de assinatura digital referente à Declaração de Recebimento de materiais. Contexto do Processo Atual Hoje, ao receber o romaneio/cópia da nota fiscal, realizamos a seguinte sequência: 1. Acessamos o sistema no menu Con</t>
-  </si>
-  <si>
-    <t>Alex Julio Estacio</t>
-  </si>
-  <si>
-    <t>Sistemas</t>
-  </si>
-  <si>
-    <t>02/04/2026</t>
-  </si>
-  <si>
-    <t>33991</t>
-  </si>
-  <si>
-    <t>Melhoria relatório 2ª corda - Gestão a vista</t>
-  </si>
-  <si>
-    <t>Boa tarde, Foi identificado um ponto de melhoria para o relatório da segunda corda com o objetivo de gerar uma tela para gestão a vista. Conforme explicado para o Flavio, segue os pontos de necessidades: - Considerar a entrada no 8890 a partir do dia 01 de cada mês. - Considerar demanda do dia o gru</t>
-  </si>
-  <si>
-    <t>Natalia De Souza</t>
-  </si>
-  <si>
-    <t>21/10/2025</t>
-  </si>
-  <si>
-    <t>34533</t>
-  </si>
-  <si>
-    <t>DESCRIÇÃO DAS OPERAÇÕES JATOS</t>
-  </si>
-  <si>
-    <t>34721</t>
-  </si>
-  <si>
-    <t>Solicitação de melhoria no WMS – Retenção de dados na pré-lista</t>
-  </si>
-  <si>
-    <t>Baixa</t>
-  </si>
-  <si>
-    <t>34894</t>
-  </si>
-  <si>
-    <t>Novos modelos para Apontamento Digital</t>
-  </si>
-  <si>
-    <t>34793</t>
-  </si>
-  <si>
-    <t>Chamado para revisão BI Manutenção - Chamado Principal</t>
-  </si>
-  <si>
-    <t>Fazendo</t>
-  </si>
-  <si>
-    <t>34723</t>
-  </si>
-  <si>
-    <t>Desenvolvimento sistema Pré-lista EPI</t>
-  </si>
-  <si>
-    <t>34377</t>
-  </si>
-  <si>
-    <t>Lógica de ACR no sistema de manutenção - Pila 2 MP - Reunião</t>
-  </si>
-  <si>
-    <t>34776</t>
-  </si>
-  <si>
-    <t>Correção informações Registro 1100</t>
-  </si>
-  <si>
-    <t>34738</t>
-  </si>
-  <si>
-    <t>ATUALIZAÇÃO DE TABELAS DO CPP22</t>
-  </si>
-  <si>
-    <t>32141</t>
-  </si>
-  <si>
-    <t>Cadastro de Embalagem no CPP</t>
-  </si>
-  <si>
-    <t>Bom dia, Flavio, Gentileza criar na tela do CPP 03 campos. * Código da Embalagem: * Dimensão: * Peso Embalagem: O preenchimento será feito de duas formas: * O histórico vamos enviar uma lista com o modelo e as informações para a atualização de todos os vigentes. * Os novos modelos o Diego irá preenc</t>
-  </si>
-  <si>
-    <t>Djalma Machado</t>
-  </si>
-  <si>
-    <t>ADH</t>
-  </si>
-  <si>
-    <t>02/06/2026</t>
-  </si>
-  <si>
-    <t>34741</t>
-  </si>
-  <si>
-    <t>Consulta movimentação - Tempo de entrega</t>
-  </si>
-  <si>
-    <t>34740</t>
-  </si>
-  <si>
-    <t>CAMPO DE OBSERVAÇÕES TRATAMENTO TÉRMICO AP119 X CPP</t>
-  </si>
-  <si>
-    <t>34742</t>
-  </si>
-  <si>
-    <t>Lista suspensa - Contentores</t>
-  </si>
-  <si>
-    <t>34336</t>
-  </si>
-  <si>
-    <t>Engenharia</t>
-  </si>
-  <si>
-    <t>DIÁRIO DE BORDO</t>
-  </si>
-  <si>
-    <t>Bom dia, Favor atualizar o sistema de Diário de Bordo [UCPP221Y] no CPP para que permita mais opções de cadastros e consultas conforme campos existentes da tela WCPP22K, exceto os riscados na imagem abaixo, e com duas opções a mais sendo "Peso Unitário" e "Tipo de Produção": At.te</t>
-  </si>
-  <si>
-    <t>Willian Gabriel Paixão dos Santos</t>
-  </si>
-  <si>
-    <t>33790</t>
-  </si>
-  <si>
-    <t>Dados divergentes tempo padrão - CPP e QlikSense</t>
-  </si>
-  <si>
-    <t>29853</t>
-  </si>
-  <si>
-    <t>WMS - Sistema de Picking - Distribuição de Estoque em carteira</t>
-  </si>
-  <si>
-    <t>Boa tarde Conforme conversamos, precisamos de um sistema dentro do WMS que faça a distribuição em tempo real do saldo do Estoque com a carteira. Conforme é realizado o faturamento, a carteira seja atualizada em tempo real, bem como a entrada e estorno do material. O sistema deve fornecer um relatóri</t>
-  </si>
-  <si>
-    <t>19/05/2026</t>
-  </si>
-  <si>
-    <t>34755</t>
-  </si>
-  <si>
-    <t>Qlik | Base de Proformas + Parcelas &amp; Registro de Cambio de Adiantamento de Proforma</t>
-  </si>
-  <si>
-    <t>33772</t>
-  </si>
-  <si>
-    <t>Melhoria no cadastramento dos tempos padrões - CPP</t>
-  </si>
-  <si>
-    <t>34689</t>
-  </si>
-  <si>
-    <t>CPPs LIGA 101XX</t>
-  </si>
-  <si>
-    <t>34693</t>
-  </si>
-  <si>
-    <t>Motivos de retrabalho da moldagem</t>
-  </si>
-  <si>
-    <t>34692</t>
-  </si>
-  <si>
-    <t>Inserir pergunta - Aplicação Check-List USINAGEM</t>
-  </si>
-  <si>
-    <t>34687</t>
-  </si>
-  <si>
-    <t>Filtro função no irog</t>
-  </si>
-  <si>
-    <t>34751</t>
-  </si>
-  <si>
-    <t>Correção</t>
-  </si>
-  <si>
-    <t>Falta de apontamentos - Aplicação IROG Usinagem</t>
-  </si>
-  <si>
-    <t>34710</t>
-  </si>
-  <si>
-    <t>Erro em OTF</t>
-  </si>
-  <si>
-    <t>34073</t>
-  </si>
-  <si>
-    <t>Callback em aplicações WEB</t>
-  </si>
-  <si>
-    <t>Implantação</t>
-  </si>
-  <si>
-    <t>34733</t>
-  </si>
-  <si>
-    <t>Melhoria WMS Materiais endereçados</t>
-  </si>
-  <si>
-    <t>33360</t>
-  </si>
-  <si>
-    <t>Auditoria MPO, PID e Checklist</t>
-  </si>
-  <si>
-    <t>34730</t>
-  </si>
-  <si>
-    <t>Melhoria no sistema de pré-lista WMS</t>
-  </si>
-  <si>
-    <t>34731</t>
-  </si>
-  <si>
-    <t>Ajuste no relatório de inventario</t>
-  </si>
-  <si>
-    <t>34729</t>
-  </si>
-  <si>
-    <t>Melhoria WMS assinatura digital</t>
-  </si>
-  <si>
-    <t>32873</t>
-  </si>
-  <si>
-    <t>Dados Pgto por Invoice</t>
-  </si>
-  <si>
-    <t>24746</t>
-  </si>
-  <si>
-    <t>Integração de faturamentos com eventos</t>
-  </si>
-  <si>
-    <t>34732</t>
-  </si>
-  <si>
-    <t>Ajuste no inventario WMS</t>
-  </si>
-  <si>
-    <t>29476</t>
-  </si>
-  <si>
-    <t>Qlik Sense - Dados Parcelas Invoice e Pgto</t>
-  </si>
-  <si>
-    <t>34665</t>
-  </si>
-  <si>
-    <t>Sistema de Consulta MPO</t>
-  </si>
-  <si>
-    <t>34109</t>
-  </si>
-  <si>
-    <t>Melhorias Sistema Manutenção</t>
-  </si>
-  <si>
-    <t>33662</t>
-  </si>
-  <si>
-    <t>Controle de documentação de exportação</t>
-  </si>
-  <si>
-    <t>34682</t>
-  </si>
-  <si>
-    <t>Registro campanha forno Arco</t>
-  </si>
-  <si>
-    <t>33632</t>
-  </si>
-  <si>
-    <t>Cálculo de carga - Sistema de corridas - Reunião</t>
-  </si>
-  <si>
-    <t>34323</t>
-  </si>
-  <si>
-    <t>Incluir informação - tela de Log Sequencias</t>
-  </si>
-  <si>
-    <t>34728</t>
-  </si>
-  <si>
-    <t>Ajustes na tela de coleta de assinatura digital</t>
-  </si>
-  <si>
-    <t>34635</t>
-  </si>
-  <si>
-    <t>Melhoria B. I.</t>
-  </si>
-  <si>
-    <t>34727</t>
-  </si>
-  <si>
-    <t>Problema na alocação de materiais no sistema de Pré-Lista Web</t>
-  </si>
-  <si>
-    <t>33333</t>
-  </si>
-  <si>
-    <t>Teste com Trigger - Checagem do fechamento do custo</t>
-  </si>
-  <si>
-    <t>Homologação</t>
-  </si>
-  <si>
-    <t>34725</t>
-  </si>
-  <si>
-    <t>Solicitação de melhoria no sistema de pré-lista web</t>
-  </si>
-  <si>
-    <t>34475</t>
-  </si>
-  <si>
-    <t>CRIAÇÃO DE FLUXO ( RETRABALHO BRUTO REB VI )</t>
-  </si>
-  <si>
-    <t>34726</t>
-  </si>
-  <si>
-    <t>Inconsistência de saldos entre WMS e ERP na pré-lista WEB</t>
-  </si>
-  <si>
-    <t>34758</t>
-  </si>
-  <si>
-    <t>Alteração na tela Gestão a Vista "Controle de PO em aberto"</t>
-  </si>
-  <si>
-    <t>34615</t>
-  </si>
-  <si>
-    <t>Inclusão de informação no momento da exclusão de NF da portaria</t>
-  </si>
-  <si>
-    <t>34549</t>
-  </si>
-  <si>
-    <t>Travamento do registro</t>
-  </si>
-  <si>
-    <t>Manter data/hora de inclusão e data/Hora de alteração.</t>
-  </si>
-  <si>
-    <t>34542</t>
-  </si>
-  <si>
-    <t>Sistema Indicadores GIQ</t>
-  </si>
-  <si>
-    <t>34432</t>
-  </si>
-  <si>
-    <t>Modificar Painel Manipuladores para APON3</t>
-  </si>
-  <si>
-    <t>20/10/2025</t>
-  </si>
-  <si>
-    <t>33130</t>
-  </si>
-  <si>
-    <t>Comercial</t>
-  </si>
-  <si>
-    <t>Integração CRM - Carga Ofertas</t>
-  </si>
-  <si>
     <t>Laura Herrmann Schmickler</t>
   </si>
   <si>
-    <t>34724</t>
+    <t>18212143383</t>
   </si>
   <si>
     <t>Solicitação de melhoria no sistema de inventário – Embalagens Magayver</t>
   </si>
   <si>
-    <t>34697</t>
+    <t>18213933520</t>
   </si>
   <si>
     <t>Conferencia de volumes NF/pre-embarque</t>
@@ -597,25 +627,31 @@
     <t>Matheus Rodrigues de Almeida</t>
   </si>
   <si>
-    <t>33660</t>
+    <t>18236204839</t>
   </si>
   <si>
     <t>Apontamento por botoeiras na Carrossel</t>
   </si>
   <si>
-    <t>34012</t>
+    <t>18236204827</t>
   </si>
   <si>
     <t>Painel de indicadores + Melhorias - Sistema Manutenção</t>
   </si>
   <si>
+    <t>18237827509</t>
+  </si>
+  <si>
     <t>Filtro máquinas críticas</t>
   </si>
   <si>
+    <t>18237831286</t>
+  </si>
+  <si>
     <t>Corrigir duplicidade de dados na base da aplicação</t>
   </si>
   <si>
-    <t>28708</t>
+    <t>18237284081</t>
   </si>
   <si>
     <t>Novo Recurso</t>
@@ -624,67 +660,76 @@
     <t>Bloco K</t>
   </si>
   <si>
+    <t>18237833234</t>
+  </si>
+  <si>
     <t>Campo calculado de % Disponibilidade / MTTR e MTBF</t>
   </si>
   <si>
-    <t>33807</t>
+    <t>18236307607</t>
   </si>
   <si>
     <t>Nome na barra de titulo da master page</t>
   </si>
   <si>
+    <t>18236318572</t>
+  </si>
+  <si>
     <t>Apresentar tempo padrão/meta</t>
   </si>
   <si>
+    <t>18236327260</t>
+  </si>
+  <si>
     <t>Selecionar cabine no login</t>
   </si>
   <si>
-    <t>33695</t>
+    <t>18243716882</t>
   </si>
   <si>
     <t>Selecionador de Componente e modo de falha - Apresentação</t>
   </si>
   <si>
-    <t>22/10/2025</t>
-  </si>
-  <si>
     <t>Semana 4</t>
   </si>
   <si>
-    <t>33412</t>
+    <t>18243716625</t>
   </si>
   <si>
     <t>Atualização de Metas - Equipamento - Apresentação</t>
   </si>
   <si>
+    <t>18243716776</t>
+  </si>
+  <si>
     <t>Atualização de Metas - Local - Apresentação</t>
   </si>
   <si>
-    <t>33867</t>
+    <t>18243716995</t>
   </si>
   <si>
     <t>Arvore de ativos na WEB - Apresentação</t>
   </si>
   <si>
+    <t>18248212026</t>
+  </si>
+  <si>
     <t>Criar API arquivos</t>
   </si>
   <si>
-    <t>34818</t>
+    <t>18253870735</t>
   </si>
   <si>
     <t>Porcentagem apontamento jato dirigido</t>
   </si>
   <si>
-    <t>23/10/2025</t>
-  </si>
-  <si>
-    <t>34375</t>
+    <t>18257047510</t>
   </si>
   <si>
     <t>Criação e novo responsável refugo</t>
   </si>
   <si>
-    <t>33009</t>
+    <t>18262247022</t>
   </si>
   <si>
     <t>Ajustes Dalca e Lianco</t>
@@ -693,15 +738,18 @@
     <t>24/10/2025</t>
   </si>
   <si>
+    <t>18262604587</t>
+  </si>
+  <si>
     <t>Ajustes Dalca e Lianco - Implementar para ter dois modelos diferentes na mesa.</t>
   </si>
   <si>
+    <t>18300106667</t>
+  </si>
+  <si>
     <t>Controle de acesso ao assistente de IA</t>
   </si>
   <si>
-    <t>29/10/2025</t>
-  </si>
-  <si>
     <t>Semana 5</t>
   </si>
   <si>
@@ -711,7 +759,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2025-22</t>
+    <t>Out/2025</t>
   </si>
   <si>
     <t>Base</t>
@@ -1344,7 +1392,7 @@
         <v>31</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>25</v>
@@ -1353,7 +1401,7 @@
         <v>26</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O3" s="2" t="s">
         <v>28</v>
@@ -1361,7 +1409,7 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>16</v>
@@ -1373,13 +1421,13 @@
         <v>18</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>21</v>
@@ -1388,10 +1436,10 @@
         <v>22</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>25</v>
@@ -1400,7 +1448,7 @@
         <v>26</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="O4" s="2" t="s">
         <v>28</v>
@@ -1408,22 +1456,22 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>20</v>
@@ -1435,10 +1483,10 @@
         <v>22</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>25</v>
@@ -1447,7 +1495,7 @@
         <v>26</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="O5" s="2" t="s">
         <v>28</v>
@@ -1455,7 +1503,7 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>16</v>
@@ -1467,10 +1515,10 @@
         <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>20</v>
@@ -1485,16 +1533,16 @@
         <v>31</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O6" s="2" t="s">
         <v>28</v>
@@ -1502,7 +1550,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>16</v>
@@ -1514,10 +1562,10 @@
         <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>20</v>
@@ -1532,7 +1580,7 @@
         <v>31</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>25</v>
@@ -1541,7 +1589,7 @@
         <v>26</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O7" s="2" t="s">
         <v>28</v>
@@ -1549,7 +1597,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
@@ -1561,10 +1609,10 @@
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>20</v>
@@ -1579,7 +1627,7 @@
         <v>31</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>25</v>
@@ -1588,7 +1636,7 @@
         <v>26</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O8" s="2" t="s">
         <v>28</v>
@@ -1596,46 +1644,46 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O9" s="2" t="s">
         <v>28</v>
@@ -1643,37 +1691,37 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>56</v>
-      </c>
       <c r="J10" s="2" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>25</v>
@@ -1682,7 +1730,7 @@
         <v>26</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O10" s="2" t="s">
         <v>28</v>
@@ -1690,7 +1738,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
@@ -1702,10 +1750,10 @@
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>20</v>
@@ -1720,7 +1768,7 @@
         <v>31</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>25</v>
@@ -1729,7 +1777,7 @@
         <v>26</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O11" s="2" t="s">
         <v>28</v>
@@ -1737,7 +1785,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
@@ -1749,13 +1797,13 @@
         <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>21</v>
@@ -1767,16 +1815,16 @@
         <v>31</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O12" s="2" t="s">
         <v>28</v>
@@ -1784,7 +1832,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>16</v>
@@ -1796,10 +1844,10 @@
         <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>20</v>
@@ -1811,10 +1859,10 @@
         <v>22</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>25</v>
@@ -1823,7 +1871,7 @@
         <v>26</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O13" s="2" t="s">
         <v>28</v>
@@ -1831,7 +1879,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
@@ -1843,13 +1891,13 @@
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>21</v>
@@ -1858,19 +1906,19 @@
         <v>22</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O14" s="2" t="s">
         <v>28</v>
@@ -1878,7 +1926,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>16</v>
@@ -1890,13 +1938,13 @@
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>21</v>
@@ -1908,16 +1956,16 @@
         <v>31</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O15" s="2" t="s">
         <v>28</v>
@@ -1925,7 +1973,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -1937,13 +1985,13 @@
         <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>21</v>
@@ -1955,7 +2003,7 @@
         <v>31</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>25</v>
@@ -1964,7 +2012,7 @@
         <v>26</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O16" s="2" t="s">
         <v>28</v>
@@ -1972,7 +2020,7 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>16</v>
@@ -1984,10 +2032,10 @@
         <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>20</v>
@@ -1999,10 +2047,10 @@
         <v>22</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>25</v>
@@ -2011,7 +2059,7 @@
         <v>26</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O17" s="2" t="s">
         <v>28</v>
@@ -2019,7 +2067,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
@@ -2031,10 +2079,10 @@
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>20</v>
@@ -2049,7 +2097,7 @@
         <v>31</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>25</v>
@@ -2058,7 +2106,7 @@
         <v>26</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O18" s="2" t="s">
         <v>28</v>
@@ -2066,37 +2114,37 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>16</v>
+        <v>85</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>25</v>
@@ -2105,7 +2153,7 @@
         <v>26</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O19" s="2" t="s">
         <v>28</v>
@@ -2113,7 +2161,7 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
@@ -2125,10 +2173,10 @@
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>20</v>
@@ -2143,7 +2191,7 @@
         <v>31</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>24</v>
+        <v>93</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>25</v>
@@ -2152,7 +2200,7 @@
         <v>26</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O20" s="2" t="s">
         <v>28</v>
@@ -2160,7 +2208,7 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>16</v>
@@ -2172,10 +2220,10 @@
         <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>20</v>
@@ -2190,7 +2238,7 @@
         <v>31</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>24</v>
+        <v>93</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>25</v>
@@ -2199,7 +2247,7 @@
         <v>26</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O21" s="2" t="s">
         <v>28</v>
@@ -2207,7 +2255,7 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>16</v>
@@ -2219,10 +2267,10 @@
         <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>20</v>
@@ -2237,7 +2285,7 @@
         <v>31</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>24</v>
+        <v>93</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>25</v>
@@ -2246,7 +2294,7 @@
         <v>26</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O22" s="2" t="s">
         <v>28</v>
@@ -2254,31 +2302,31 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>31</v>
@@ -2287,13 +2335,13 @@
         <v>24</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O23" s="2" t="s">
         <v>28</v>
@@ -2301,7 +2349,7 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
@@ -2313,10 +2361,10 @@
         <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>20</v>
@@ -2331,7 +2379,7 @@
         <v>31</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>25</v>
@@ -2340,7 +2388,7 @@
         <v>26</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O24" s="2" t="s">
         <v>28</v>
@@ -2348,46 +2396,46 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>16</v>
+        <v>85</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O25" s="2" t="s">
         <v>28</v>
@@ -2395,7 +2443,7 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>16</v>
@@ -2407,13 +2455,13 @@
         <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>21</v>
@@ -2425,7 +2473,7 @@
         <v>31</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>24</v>
+        <v>111</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>25</v>
@@ -2434,7 +2482,7 @@
         <v>26</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O26" s="2" t="s">
         <v>28</v>
@@ -2442,7 +2490,7 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>16</v>
@@ -2454,13 +2502,13 @@
         <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>21</v>
@@ -2469,10 +2517,10 @@
         <v>22</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>25</v>
@@ -2481,7 +2529,7 @@
         <v>26</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O27" s="2" t="s">
         <v>28</v>
@@ -2489,7 +2537,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>16</v>
@@ -2501,10 +2549,10 @@
         <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>20</v>
@@ -2519,7 +2567,7 @@
         <v>31</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>25</v>
@@ -2528,7 +2576,7 @@
         <v>26</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O28" s="2" t="s">
         <v>28</v>
@@ -2536,7 +2584,7 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>16</v>
@@ -2548,10 +2596,10 @@
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>20</v>
@@ -2566,7 +2614,7 @@
         <v>31</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>25</v>
@@ -2575,7 +2623,7 @@
         <v>26</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O29" s="2" t="s">
         <v>28</v>
@@ -2583,7 +2631,7 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>16</v>
@@ -2595,10 +2643,10 @@
         <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>20</v>
@@ -2613,7 +2661,7 @@
         <v>31</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>25</v>
@@ -2622,7 +2670,7 @@
         <v>26</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O30" s="2" t="s">
         <v>28</v>
@@ -2630,7 +2678,7 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>16</v>
@@ -2642,10 +2690,10 @@
         <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>20</v>
@@ -2660,7 +2708,7 @@
         <v>31</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>25</v>
@@ -2669,7 +2717,7 @@
         <v>26</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O31" s="2" t="s">
         <v>28</v>
@@ -2677,22 +2725,22 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>20</v>
@@ -2707,7 +2755,7 @@
         <v>31</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>25</v>
@@ -2716,7 +2764,7 @@
         <v>26</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O32" s="2" t="s">
         <v>28</v>
@@ -2724,22 +2772,22 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>20</v>
@@ -2754,7 +2802,7 @@
         <v>31</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>25</v>
@@ -2763,7 +2811,7 @@
         <v>26</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O33" s="2" t="s">
         <v>28</v>
@@ -2771,7 +2819,7 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>16</v>
@@ -2783,10 +2831,10 @@
         <v>18</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>20</v>
@@ -2798,19 +2846,19 @@
         <v>22</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>24</v>
+        <v>129</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="M34" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O34" s="2" t="s">
         <v>28</v>
@@ -2818,7 +2866,7 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>16</v>
@@ -2830,13 +2878,13 @@
         <v>18</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>21</v>
@@ -2848,7 +2896,7 @@
         <v>31</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L35" s="2" t="s">
         <v>25</v>
@@ -2857,7 +2905,7 @@
         <v>26</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O35" s="2" t="s">
         <v>28</v>
@@ -2865,22 +2913,22 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>20</v>
@@ -2895,7 +2943,7 @@
         <v>31</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>24</v>
+        <v>135</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>25</v>
@@ -2904,7 +2952,7 @@
         <v>26</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O36" s="2" t="s">
         <v>28</v>
@@ -2912,7 +2960,7 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>16</v>
@@ -2924,13 +2972,13 @@
         <v>18</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>21</v>
@@ -2942,7 +2990,7 @@
         <v>31</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>24</v>
+        <v>129</v>
       </c>
       <c r="L37" s="2" t="s">
         <v>25</v>
@@ -2951,7 +2999,7 @@
         <v>26</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O37" s="2" t="s">
         <v>28</v>
@@ -2959,7 +3007,7 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>16</v>
@@ -2971,13 +3019,13 @@
         <v>18</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>21</v>
@@ -2998,7 +3046,7 @@
         <v>26</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O38" s="2" t="s">
         <v>28</v>
@@ -3006,7 +3054,7 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>16</v>
@@ -3018,13 +3066,13 @@
         <v>18</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>21</v>
@@ -3036,7 +3084,7 @@
         <v>31</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>24</v>
+        <v>129</v>
       </c>
       <c r="L39" s="2" t="s">
         <v>25</v>
@@ -3045,7 +3093,7 @@
         <v>26</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O39" s="2" t="s">
         <v>28</v>
@@ -3053,7 +3101,7 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>16</v>
@@ -3065,13 +3113,13 @@
         <v>18</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>21</v>
@@ -3083,7 +3131,7 @@
         <v>31</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>24</v>
+        <v>111</v>
       </c>
       <c r="L40" s="2" t="s">
         <v>25</v>
@@ -3092,7 +3140,7 @@
         <v>26</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O40" s="2" t="s">
         <v>28</v>
@@ -3100,22 +3148,22 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>20</v>
@@ -3127,19 +3175,19 @@
         <v>22</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O41" s="2" t="s">
         <v>28</v>
@@ -3147,7 +3195,7 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>16</v>
@@ -3159,13 +3207,13 @@
         <v>18</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>21</v>
@@ -3177,7 +3225,7 @@
         <v>31</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L42" s="2" t="s">
         <v>25</v>
@@ -3186,7 +3234,7 @@
         <v>26</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O42" s="2" t="s">
         <v>28</v>
@@ -3194,7 +3242,7 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>16</v>
@@ -3206,13 +3254,13 @@
         <v>18</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>21</v>
@@ -3224,7 +3272,7 @@
         <v>31</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>24</v>
+        <v>111</v>
       </c>
       <c r="L43" s="2" t="s">
         <v>25</v>
@@ -3233,7 +3281,7 @@
         <v>26</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O43" s="2" t="s">
         <v>28</v>
@@ -3241,7 +3289,7 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>16</v>
@@ -3253,10 +3301,10 @@
         <v>18</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>20</v>
@@ -3271,16 +3319,16 @@
         <v>31</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="M44" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O44" s="2" t="s">
         <v>28</v>
@@ -3288,7 +3336,7 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>16</v>
@@ -3300,10 +3348,10 @@
         <v>18</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>20</v>
@@ -3315,10 +3363,10 @@
         <v>22</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L45" s="2" t="s">
         <v>25</v>
@@ -3327,7 +3375,7 @@
         <v>26</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O45" s="2" t="s">
         <v>28</v>
@@ -3335,7 +3383,7 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>16</v>
@@ -3347,10 +3395,10 @@
         <v>18</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>20</v>
@@ -3362,10 +3410,10 @@
         <v>22</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>24</v>
+        <v>93</v>
       </c>
       <c r="L46" s="2" t="s">
         <v>25</v>
@@ -3374,7 +3422,7 @@
         <v>26</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O46" s="2" t="s">
         <v>28</v>
@@ -3382,7 +3430,7 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>16</v>
@@ -3394,10 +3442,10 @@
         <v>18</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>20</v>
@@ -3412,16 +3460,16 @@
         <v>31</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O47" s="2" t="s">
         <v>28</v>
@@ -3429,7 +3477,7 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>16</v>
@@ -3441,10 +3489,10 @@
         <v>18</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>20</v>
@@ -3456,19 +3504,19 @@
         <v>22</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O48" s="2" t="s">
         <v>28</v>
@@ -3476,7 +3524,7 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>16</v>
@@ -3488,10 +3536,10 @@
         <v>18</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>20</v>
@@ -3503,10 +3551,10 @@
         <v>22</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="L49" s="2" t="s">
         <v>25</v>
@@ -3515,7 +3563,7 @@
         <v>26</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O49" s="2" t="s">
         <v>28</v>
@@ -3523,7 +3571,7 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>16</v>
@@ -3535,13 +3583,13 @@
         <v>18</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>21</v>
@@ -3553,7 +3601,7 @@
         <v>31</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L50" s="2" t="s">
         <v>25</v>
@@ -3562,7 +3610,7 @@
         <v>26</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O50" s="2" t="s">
         <v>28</v>
@@ -3570,7 +3618,7 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>16</v>
@@ -3582,10 +3630,10 @@
         <v>18</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>20</v>
@@ -3600,16 +3648,16 @@
         <v>31</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O51" s="2" t="s">
         <v>28</v>
@@ -3617,7 +3665,7 @@
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>16</v>
@@ -3629,13 +3677,13 @@
         <v>18</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>21</v>
@@ -3647,16 +3695,16 @@
         <v>31</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O52" s="2" t="s">
         <v>28</v>
@@ -3664,7 +3712,7 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>16</v>
@@ -3676,10 +3724,10 @@
         <v>18</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>20</v>
@@ -3691,19 +3739,19 @@
         <v>22</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O53" s="2" t="s">
         <v>28</v>
@@ -3711,7 +3759,7 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>16</v>
@@ -3723,13 +3771,13 @@
         <v>18</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>21</v>
@@ -3750,7 +3798,7 @@
         <v>26</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O54" s="2" t="s">
         <v>28</v>
@@ -3758,7 +3806,7 @@
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>16</v>
@@ -3770,10 +3818,10 @@
         <v>18</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>20</v>
@@ -3785,10 +3833,10 @@
         <v>22</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L55" s="2" t="s">
         <v>25</v>
@@ -3797,7 +3845,7 @@
         <v>26</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O55" s="2" t="s">
         <v>28</v>
@@ -3805,7 +3853,7 @@
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>16</v>
@@ -3817,13 +3865,13 @@
         <v>18</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>21</v>
@@ -3835,16 +3883,16 @@
         <v>31</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O56" s="2" t="s">
         <v>28</v>
@@ -3852,7 +3900,7 @@
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>16</v>
@@ -3864,10 +3912,10 @@
         <v>18</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>20</v>
@@ -3882,7 +3930,7 @@
         <v>31</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L57" s="2" t="s">
         <v>25</v>
@@ -3891,7 +3939,7 @@
         <v>26</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O57" s="2" t="s">
         <v>28</v>
@@ -3899,7 +3947,7 @@
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>16</v>
@@ -3911,10 +3959,10 @@
         <v>18</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>20</v>
@@ -3929,7 +3977,7 @@
         <v>31</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>24</v>
+        <v>129</v>
       </c>
       <c r="L58" s="2" t="s">
         <v>25</v>
@@ -3938,7 +3986,7 @@
         <v>26</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O58" s="2" t="s">
         <v>28</v>
@@ -3946,7 +3994,7 @@
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>16</v>
@@ -3958,10 +4006,10 @@
         <v>18</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>20</v>
@@ -3976,16 +4024,16 @@
         <v>31</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="M59" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O59" s="2" t="s">
         <v>28</v>
@@ -3993,7 +4041,7 @@
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>160</v>
+        <v>183</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>16</v>
@@ -4005,10 +4053,10 @@
         <v>18</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>20</v>
@@ -4020,19 +4068,19 @@
         <v>22</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O60" s="2" t="s">
         <v>28</v>
@@ -4040,7 +4088,7 @@
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>16</v>
@@ -4052,10 +4100,10 @@
         <v>18</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>20</v>
@@ -4070,7 +4118,7 @@
         <v>31</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>24</v>
+        <v>187</v>
       </c>
       <c r="L61" s="2" t="s">
         <v>25</v>
@@ -4079,7 +4127,7 @@
         <v>26</v>
       </c>
       <c r="N61" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O61" s="2" t="s">
         <v>28</v>
@@ -4087,7 +4135,7 @@
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>16</v>
@@ -4099,10 +4147,10 @@
         <v>18</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>20</v>
@@ -4114,19 +4162,19 @@
         <v>22</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>180</v>
+        <v>38</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M62" s="2" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O62" s="2" t="s">
         <v>28</v>
@@ -4134,37 +4182,37 @@
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>24</v>
+        <v>193</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L63" s="2" t="s">
         <v>25</v>
@@ -4173,7 +4221,7 @@
         <v>26</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O63" s="2" t="s">
         <v>28</v>
@@ -4181,7 +4229,7 @@
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>16</v>
@@ -4193,10 +4241,10 @@
         <v>18</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>20</v>
@@ -4211,7 +4259,7 @@
         <v>31</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="L64" s="2" t="s">
         <v>25</v>
@@ -4220,7 +4268,7 @@
         <v>26</v>
       </c>
       <c r="N64" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O64" s="2" t="s">
         <v>28</v>
@@ -4228,7 +4276,7 @@
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>16</v>
@@ -4240,10 +4288,10 @@
         <v>18</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>20</v>
@@ -4258,16 +4306,16 @@
         <v>31</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>24</v>
+        <v>135</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="M65" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N65" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O65" s="2" t="s">
         <v>28</v>
@@ -4275,34 +4323,34 @@
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="K66" s="2" t="s">
         <v>24</v>
@@ -4314,7 +4362,7 @@
         <v>26</v>
       </c>
       <c r="N66" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O66" s="2" t="s">
         <v>28</v>
@@ -4322,7 +4370,7 @@
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>16</v>
@@ -4334,10 +4382,10 @@
         <v>18</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>20</v>
@@ -4349,19 +4397,19 @@
         <v>22</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L67" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M67" s="2" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="N67" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O67" s="2" t="s">
         <v>28</v>
@@ -4369,7 +4417,7 @@
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>16</v>
@@ -4381,10 +4429,10 @@
         <v>18</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>20</v>
@@ -4396,19 +4444,19 @@
         <v>22</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M68" s="2" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="N68" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O68" s="2" t="s">
         <v>28</v>
@@ -4416,7 +4464,7 @@
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>70</v>
+        <v>208</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>16</v>
@@ -4428,13 +4476,13 @@
         <v>18</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H69" s="2" t="s">
         <v>21</v>
@@ -4443,10 +4491,10 @@
         <v>22</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="L69" s="2" t="s">
         <v>25</v>
@@ -4455,7 +4503,7 @@
         <v>26</v>
       </c>
       <c r="N69" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O69" s="2" t="s">
         <v>28</v>
@@ -4463,7 +4511,7 @@
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>70</v>
+        <v>210</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>16</v>
@@ -4475,13 +4523,13 @@
         <v>18</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H70" s="2" t="s">
         <v>21</v>
@@ -4490,19 +4538,19 @@
         <v>22</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="N70" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O70" s="2" t="s">
         <v>28</v>
@@ -4510,25 +4558,25 @@
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H71" s="2" t="s">
         <v>21</v>
@@ -4537,10 +4585,10 @@
         <v>22</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>24</v>
+        <v>129</v>
       </c>
       <c r="L71" s="2" t="s">
         <v>25</v>
@@ -4549,7 +4597,7 @@
         <v>26</v>
       </c>
       <c r="N71" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O71" s="2" t="s">
         <v>28</v>
@@ -4557,7 +4605,7 @@
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>70</v>
+        <v>215</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>16</v>
@@ -4569,13 +4617,13 @@
         <v>18</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>21</v>
@@ -4584,19 +4632,19 @@
         <v>22</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M72" s="2" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="N72" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O72" s="2" t="s">
         <v>28</v>
@@ -4604,7 +4652,7 @@
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>16</v>
@@ -4616,10 +4664,10 @@
         <v>18</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>20</v>
@@ -4631,7 +4679,7 @@
         <v>22</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="K73" s="2" t="s">
         <v>24</v>
@@ -4643,7 +4691,7 @@
         <v>26</v>
       </c>
       <c r="N73" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O73" s="2" t="s">
         <v>28</v>
@@ -4651,7 +4699,7 @@
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>16</v>
@@ -4663,10 +4711,10 @@
         <v>18</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>206</v>
+        <v>220</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>206</v>
+        <v>220</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>20</v>
@@ -4678,7 +4726,7 @@
         <v>22</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="K74" s="2" t="s">
         <v>24</v>
@@ -4690,7 +4738,7 @@
         <v>26</v>
       </c>
       <c r="N74" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O74" s="2" t="s">
         <v>28</v>
@@ -4698,7 +4746,7 @@
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>16</v>
@@ -4710,10 +4758,10 @@
         <v>18</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>207</v>
+        <v>222</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>207</v>
+        <v>222</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>20</v>
@@ -4725,7 +4773,7 @@
         <v>22</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="K75" s="2" t="s">
         <v>24</v>
@@ -4737,7 +4785,7 @@
         <v>26</v>
       </c>
       <c r="N75" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O75" s="2" t="s">
         <v>28</v>
@@ -4745,7 +4793,7 @@
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>16</v>
@@ -4757,10 +4805,10 @@
         <v>18</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>20</v>
@@ -4772,10 +4820,10 @@
         <v>22</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>210</v>
+        <v>93</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="L76" s="2" t="s">
         <v>25</v>
@@ -4784,7 +4832,7 @@
         <v>26</v>
       </c>
       <c r="N76" s="2" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="O76" s="2" t="s">
         <v>28</v>
@@ -4792,7 +4840,7 @@
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>16</v>
@@ -4804,10 +4852,10 @@
         <v>18</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>20</v>
@@ -4819,10 +4867,10 @@
         <v>22</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>210</v>
+        <v>93</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>24</v>
+        <v>111</v>
       </c>
       <c r="L77" s="2" t="s">
         <v>25</v>
@@ -4831,7 +4879,7 @@
         <v>26</v>
       </c>
       <c r="N77" s="2" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="O77" s="2" t="s">
         <v>28</v>
@@ -4839,7 +4887,7 @@
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>212</v>
+        <v>228</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>16</v>
@@ -4851,10 +4899,10 @@
         <v>18</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>214</v>
+        <v>229</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>214</v>
+        <v>229</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>20</v>
@@ -4866,10 +4914,10 @@
         <v>22</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>210</v>
+        <v>93</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>24</v>
+        <v>111</v>
       </c>
       <c r="L78" s="2" t="s">
         <v>25</v>
@@ -4878,7 +4926,7 @@
         <v>26</v>
       </c>
       <c r="N78" s="2" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="O78" s="2" t="s">
         <v>28</v>
@@ -4886,7 +4934,7 @@
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>215</v>
+        <v>230</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>16</v>
@@ -4898,10 +4946,10 @@
         <v>18</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>216</v>
+        <v>231</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>216</v>
+        <v>231</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>20</v>
@@ -4913,10 +4961,10 @@
         <v>22</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>210</v>
+        <v>93</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>24</v>
+        <v>93</v>
       </c>
       <c r="L79" s="2" t="s">
         <v>25</v>
@@ -4925,7 +4973,7 @@
         <v>26</v>
       </c>
       <c r="N79" s="2" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="O79" s="2" t="s">
         <v>28</v>
@@ -4933,22 +4981,22 @@
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>68</v>
+        <v>232</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>20</v>
@@ -4960,10 +5008,10 @@
         <v>22</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>210</v>
+        <v>93</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>24</v>
+        <v>111</v>
       </c>
       <c r="L80" s="2" t="s">
         <v>25</v>
@@ -4972,7 +5020,7 @@
         <v>26</v>
       </c>
       <c r="N80" s="2" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="O80" s="2" t="s">
         <v>28</v>
@@ -4980,7 +5028,7 @@
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>218</v>
+        <v>234</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>16</v>
@@ -4992,10 +5040,10 @@
         <v>18</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>219</v>
+        <v>235</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>219</v>
+        <v>235</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>20</v>
@@ -5007,10 +5055,10 @@
         <v>22</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>220</v>
+        <v>111</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>24</v>
+        <v>93</v>
       </c>
       <c r="L81" s="2" t="s">
         <v>25</v>
@@ -5019,7 +5067,7 @@
         <v>26</v>
       </c>
       <c r="N81" s="2" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="O81" s="2" t="s">
         <v>28</v>
@@ -5027,7 +5075,7 @@
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>16</v>
@@ -5039,10 +5087,10 @@
         <v>18</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>20</v>
@@ -5054,10 +5102,10 @@
         <v>22</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>220</v>
+        <v>111</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="L82" s="2" t="s">
         <v>25</v>
@@ -5066,7 +5114,7 @@
         <v>26</v>
       </c>
       <c r="N82" s="2" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="O82" s="2" t="s">
         <v>28</v>
@@ -5074,22 +5122,22 @@
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>223</v>
+        <v>238</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>20</v>
@@ -5101,19 +5149,19 @@
         <v>22</v>
       </c>
       <c r="J83" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="K83" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="L83" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M83" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N83" s="2" t="s">
         <v>225</v>
-      </c>
-      <c r="K83" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L83" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M83" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N83" s="2" t="s">
-        <v>211</v>
       </c>
       <c r="O83" s="2" t="s">
         <v>28</v>
@@ -5121,22 +5169,22 @@
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>20</v>
@@ -5148,19 +5196,19 @@
         <v>22</v>
       </c>
       <c r="J84" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="K84" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="L84" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M84" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N84" s="2" t="s">
         <v>225</v>
-      </c>
-      <c r="K84" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L84" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M84" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N84" s="2" t="s">
-        <v>211</v>
       </c>
       <c r="O84" s="2" t="s">
         <v>28</v>
@@ -5168,22 +5216,22 @@
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>121</v>
+        <v>243</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>227</v>
+        <v>244</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>227</v>
+        <v>244</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>20</v>
@@ -5195,10 +5243,10 @@
         <v>22</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>228</v>
+        <v>129</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="L85" s="2" t="s">
         <v>25</v>
@@ -5207,7 +5255,7 @@
         <v>26</v>
       </c>
       <c r="N85" s="2" t="s">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="O85" s="2" t="s">
         <v>28</v>
@@ -5226,23 +5274,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>231</v>
+        <v>247</v>
       </c>
       <c r="B2" t="s">
-        <v>232</v>
+        <v>248</v>
       </c>
       <c r="D2" t="s">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="E2" t="s">
-        <v>234</v>
+        <v>250</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -5250,16 +5298,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>235</v>
+        <v>251</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>236</v>
+        <v>252</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>237</v>
+        <v>253</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>238</v>
+        <v>254</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -5270,15 +5318,15 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>224</v>
+        <v>10.06</v>
       </c>
       <c r="J5" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>239</v>
+        <v>255</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -5291,7 +5339,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="K23">
         <v>4</v>
@@ -5299,7 +5347,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>240</v>
+        <v>256</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -5330,12 +5378,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>241</v>
+        <v>257</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>235</v>
+        <v>251</v>
       </c>
       <c r="B2">
         <v>84</v>
@@ -5349,35 +5397,35 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>224</v>
+        <v>10.06</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>242</v>
+        <v>258</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>243</v>
+        <v>259</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>244</v>
+        <v>260</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>245</v>
+        <v>261</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>246</v>
+        <v>262</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>247</v>
+        <v>263</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -5385,7 +5433,7 @@
         <v>16</v>
       </c>
       <c r="B10">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D10" t="s">
         <v>17</v>
@@ -5394,13 +5442,13 @@
         <v>72</v>
       </c>
       <c r="G10" t="s">
-        <v>248</v>
+        <v>264</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>249</v>
+        <v>265</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -5415,24 +5463,24 @@
         <v>27</v>
       </c>
       <c r="Q10">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="B11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E11">
         <v>8</v>
       </c>
       <c r="G11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H11">
         <v>16</v>
@@ -5441,30 +5489,30 @@
         <v>26</v>
       </c>
       <c r="K11">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="M11" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="N11">
         <v>14</v>
       </c>
       <c r="P11" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="Q11">
-        <v>2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>94</v>
+        <v>53</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
       <c r="D12" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="E12">
         <v>3</v>
@@ -5476,85 +5524,85 @@
         <v>57</v>
       </c>
       <c r="J12" t="s">
-        <v>250</v>
+        <v>266</v>
       </c>
       <c r="K12">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>251</v>
+        <v>267</v>
       </c>
       <c r="N12">
         <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>32</v>
+        <v>225</v>
       </c>
       <c r="Q12">
-        <v>50</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>182</v>
+        <v>99</v>
       </c>
       <c r="B13">
         <v>1</v>
       </c>
       <c r="D13" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="E13">
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H13">
         <v>11</v>
       </c>
       <c r="M13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N13">
         <v>4</v>
       </c>
       <c r="P13" t="s">
-        <v>211</v>
+        <v>245</v>
       </c>
       <c r="Q13">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B14">
         <v>1</v>
       </c>
       <c r="G14" t="s">
-        <v>252</v>
+        <v>268</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="M14" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="N14">
         <v>4</v>
       </c>
-      <c r="P14" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q14">
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>200</v>
+      </c>
+      <c r="B15">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="N15">
         <v>2</v>
@@ -5562,7 +5610,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>253</v>
+        <v>269</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -5570,7 +5618,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>254</v>
+        <v>270</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -5578,10 +5626,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -5589,7 +5637,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>256</v>
+        <v>272</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -5597,142 +5645,142 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F21" s="2">
-        <v>209</v>
+        <v>243</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>82</v>
+        <v>45</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="F22" s="2">
-        <v>0</v>
+        <v>243</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>29</v>
+        <v>66</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F23" s="2">
-        <v>0</v>
+        <v>243</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>30</v>
+        <v>67</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>33</v>
+        <v>71</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="2">
-        <v>0</v>
+        <v>243</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>34</v>
+        <v>72</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="2">
-        <v>0</v>
+        <v>243</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>40</v>
+        <v>76</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>46</v>
+        <v>98</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>16</v>
+        <v>99</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>243</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>47</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>48</v>
+        <v>105</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>16</v>
+        <v>85</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>243</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>49</v>
+        <v>106</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>58</v>
+        <v>144</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>243</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>59</v>
+        <v>145</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>63</v>
+        <v>156</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>243</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>64</v>
+        <v>157</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>68</v>
+        <v>158</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>243</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>69</v>
+        <v>159</v>
       </c>
     </row>
   </sheetData>
